--- a/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson. Maman dit : fini. L'adulte dit fini. Apolline écoute. Elle va éteindre. Apolline éteint. L'écran devient noir. Elle pose la tablette. Maman dit : on prend un autre jeu. Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon. Apolline dit : l'écran est éteint. Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
+          <t>Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson. Fini. L'adulte dit fini. Apolline écoute. Elle va éteindre. Apolline éteint. L'écran devient noir. Elle pose la tablette. On prend un autre jeu. Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon. L'écran est éteint. Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson.
+maman|Fini. L'adulte dit fini.
+narrateur|Apolline écoute. Elle va éteindre. Apolline éteint. L'écran devient noir. Elle pose la tablette.
+maman|On prend un autre jeu.
+narrateur|Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon.
+enfant-f|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Apolline ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maman a dit fini. Apolline a éteint. Elle a pris un autre jeu. La pâte, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le petit pain repose. Apolline dit merci à maman. La cuisine est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Maman dit fini. Que fait Apolline ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Maman a dit fini. Apolline a éteint. Elle a pris un autre jeu. La pâte, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Le petit pain repose. Apolline dit merci à maman. La cuisine est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apolline éteint et pétrit</t>
+          <t>La pâte molle</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon traverse la farine. Une chanson sort de la tablette. Maman dit fini. Chouchou éteint. Ils pétrissent la pâte. Un petit pain tout rond.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson. Fini. L'adulte dit fini. Apolline écoute. Elle va éteindre. Apolline éteint. L'écran devient noir. Elle pose la tablette. On prend un autre jeu. Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon. L'écran est éteint. Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
+          <t>Un rayon traverse la farine. La farine fait un petit nuage. La cuillère en bois attend. Une chanson sort de la tablette. Chouchou vit ici, avec maman. Papa est au jardin, tout près. La cuisine sent le pain. En ce moment, l'écran est allumé. Des couleurs bougent. Chouchou écoute la chanson. Chouchou. Fini. Chouchou écoute. Il va éteindre. Il éteint. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. On prend un autre jeu. Tu vas choisir ? La pâte. La pâte est molle. Elle est un peu froide. Ils pétrissent. La farine sent bon. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Tu as les mains farineuses ? Oui, maman. C'est doux. Ils font un petit pain. Le petit pain est tout rond. On range la farine ? Chouchou pousse le bol. Maman range la cuillère. Merci, maman. Merci, Chouchou. Tu as éteint. Tu as choisi un autre jeu. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1325,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson.
-maman|Fini. L'adulte dit fini.
-narrateur|Apolline écoute. Elle va éteindre. Apolline éteint. L'écran devient noir. Elle pose la tablette.
+          <t>narrateur|Un rayon traverse la farine.
+narrateur|La farine fait un petit nuage.
+narrateur|La cuillère en bois attend.
+narrateur|Une chanson sort de la tablette.
+narrateur|Chouchou vit ici, avec maman.
+narrateur|Papa est au jardin, tout près.
+narrateur|La cuisine sent le pain.
+narrateur|En ce moment, l'écran est allumé.
+narrateur|Des couleurs bougent.
+narrateur|Chouchou écoute la chanson.
+maman|Chouchou.
+maman|Fini.
+narrateur|Chouchou écoute.
+narrateur|Il va éteindre.
+narrateur|Il éteint.
+narrateur|L'écran devient noir.
+narrateur|Il pose la tablette.
+maman|Bravo, Chouchou.
+maman|Tu as éteint.
 maman|On prend un autre jeu.
-narrateur|Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon.
-enfant-f|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Tu vas choisir ?
+enfant-m|La pâte.
+narrateur|La pâte est molle.
+narrateur|Elle est un peu froide.
+narrateur|Ils pétrissent.
+narrateur|La farine sent bon.
+enfant-m|L'écran est éteint.
+maman|Oui.
+maman|Un autre jeu, c'est bien.
+maman|Bravo.
+maman|Tu as les mains farineuses ?
+enfant-m|Oui, maman.
+enfant-m|C'est doux.
+narrateur|Ils font un petit pain.
+narrateur|Le petit pain est tout rond.
+maman|On range la farine ?
+narrateur|Chouchou pousse le bol.
+narrateur|Maman range la cuillère.
+enfant-m|Merci, maman.
+maman|Merci, Chouchou.
+maman|Tu as éteint.
+maman|Tu as choisi un autre jeu.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pate,farine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman dit fini. Que fait Apolline ?</t>
+          <t>Maman dit fini. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman dit fini. Que fait Apolline ?</t>
+          <t>narrateur|Maman dit fini.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. Apolline a éteint. Elle a pris un autre jeu. La pâte, c'était bien.</t>
+          <t>Maman a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris la pâte. Bravo, Chouchou. Quand on dit fini, on éteint. Puis on prend un autre jeu. La pâte, c'était bien. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1728,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maman a dit fini. Apolline a éteint. Elle a pris un autre jeu. La pâte, c'était bien.</t>
+          <t>narrateur|Maman a dit fini.
+narrateur|Chouchou a éteint.
+narrateur|Il a pris un autre jeu.
+maman|Tu as éteint ?
+enfant-m|Oui, maman.
+enfant-m|J'ai pris la pâte.
+maman|Bravo, Chouchou.
+maman|Quand on dit fini, on éteint.
+maman|Puis on prend un autre jeu.
+narrateur|La pâte, c'était bien.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le petit pain repose. Apolline dit merci à maman. La cuisine est calme.</t>
+          <t>Le petit pain repose. Il est tout rond, tout blanc. Merci, maman. Merci, Chouchou. La cuisine est calme. On reste encore un peu ? Oui. Un peu de farine brille encore. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1902,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le petit pain repose. Apolline dit merci à maman. La cuisine est calme.</t>
+          <t>narrateur|Le petit pain repose.
+narrateur|Il est tout rond, tout blanc.
+enfant-m|Merci, maman.
+maman|Merci, Chouchou.
+narrateur|La cuisine est calme.
+maman|On reste encore un peu ?
+enfant-m|Oui.
+narrateur|Un peu de farine brille encore.
+maman|Tu as éteint.
+maman|Tu as choisi un autre jeu.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Maman a dit fini. J'ai éteint. On a pétri la pâte. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2080,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Maman a dit fini.
+enfant-m|J'ai éteint.
+enfant-m|On a pétri la pâte.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon traverse la farine. La farine fait un petit nuage. La cuillère en bois attend. Une chanson sort de la tablette. Chouchou vit ici, avec maman. Papa est au jardin, tout près. La cuisine sent le pain. En ce moment, l'écran est allumé. Des couleurs bougent. Chouchou écoute la chanson. Chouchou. Fini. Chouchou écoute. Il va éteindre. Il éteint. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. On prend un autre jeu. Tu vas choisir ? La pâte. La pâte est molle. Elle est un peu froide. Ils pétrissent. La farine sent bon. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Tu as les mains farineuses ? Oui, maman. C'est doux. Ils font un petit pain. Le petit pain est tout rond. On range la farine ? Chouchou pousse le bol. Maman range la cuillère. Merci, maman. Merci, Chouchou. Tu as éteint. Tu as choisi un autre jeu. C'est du bon travail.</t>
+          <t>Un rayon traverse la farine. La farine fait un petit nuage. La cuillère en bois attend. Une chanson sort de la tablette. Chouchou vit ici, avec maman. Papa est au jardin, tout près. La cuisine sent le pain. Le bois de la table a des lignes. Chouchou les suit du doigt. La chanson sort encore de l'écran. Des couleurs bougent. Chouchou regarde. Chouchou. Fini. Chouchou écoute. Il va éteindre. Il éteint. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. On prend un autre jeu. Tu vas choisir ? La pâte. La pâte est molle. Elle est un peu froide. Chouchou appuie avec les paumes. La pâte fait un petit bruit. Tu la roules ? Oui. Un petit serpent. Puis une boule. Ils pétrissent. La farine sent bon. L'écran est éteint. Oui. La pâte, c'est un beau jeu. Bravo. Tu as les mains farineuses ? Oui, maman. C'est doux. Ils font un petit pain. Le petit pain est tout rond. Il ressemble à une lune. Une petite lune. Oui. Un oiseau chante dehors. Tu as entendu l'oiseau ? Oui, maman. On range la farine ? Chouchou pousse le bol. Maman range la cuillère. Merci, maman. Merci, Chouchou. Tu as éteint. Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Apolline est dans la cuisine. Maman est là. Un petit écran est allumé. Des couleurs bougent. Apolline entend une chanson. Maman dit : fini. L'adulte dit fini. Apolline écoute. Elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Apolline éteint. L'écran devient noir. Elle pose la tablette. Maman dit : on prend un autre jeu. Apolline choisit la pâte. La pâte est molle. Elles pétrissent. La farine sent bon. Apolline dit : l'écran est éteint. Un autre jeu, c'est bien. Maman sourit. Elles font un petit pain. Puis elles rangent. Apolline a éteint. Elle a choisi un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon traverse la farine. La farine fait un petit nuage. La cuillère en bois attend. Une chanson sort de la tablette. Chouchou vit ici, avec maman. Papa est au jardin, tout près. La cuisine sent le pain. Le bois de la table a des lignes. Chouchou les suit du doigt. La chanson sort encore de l'écran. Des couleurs bougent. Chouchou regarde. Chouchou. Fini. Chouchou écoute. Il va éteindre. Il éteint. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. On prend un autre jeu. Tu vas choisir ? La pâte. La pâte est molle. Elle est un peu froide. Chouchou appuie avec les paumes. La pâte fait un petit bruit. Tu la roules ? Oui. Un petit serpent. Puis une boule. Ils pétrissent. La farine sent bon. L'écran est éteint. Oui. La pâte, c'est un beau jeu. Bravo. Tu as les mains farineuses ? Oui, maman. C'est doux. Ils font un petit pain. Le petit pain est tout rond. Il ressemble à une lune. Une petite lune. Oui. Un oiseau chante dehors. Tu as entendu l'oiseau ? Oui, maman. On range la farine ? Chouchou pousse le bol. Maman range la cuillère. Merci, maman. Merci, Chouchou. Tu as éteint. Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1332,9 +1332,11 @@
 narrateur|Chouchou vit ici, avec maman.
 narrateur|Papa est au jardin, tout près.
 narrateur|La cuisine sent le pain.
-narrateur|En ce moment, l'écran est allumé.
+narrateur|Le bois de la table a des lignes.
+narrateur|Chouchou les suit du doigt.
+narrateur|La chanson sort encore de l'écran.
 narrateur|Des couleurs bougent.
-narrateur|Chouchou écoute la chanson.
+narrateur|Chouchou regarde.
 maman|Chouchou.
 maman|Fini.
 narrateur|Chouchou écoute.
@@ -1349,25 +1351,36 @@
 enfant-m|La pâte.
 narrateur|La pâte est molle.
 narrateur|Elle est un peu froide.
+narrateur|Chouchou appuie avec les paumes.
+narrateur|La pâte fait un petit bruit.
+maman|Tu la roules ?
+enfant-m|Oui.
+enfant-m|Un petit serpent.
+maman|Puis une boule.
 narrateur|Ils pétrissent.
 narrateur|La farine sent bon.
 enfant-m|L'écran est éteint.
 maman|Oui.
-maman|Un autre jeu, c'est bien.
+maman|La pâte, c'est un beau jeu.
 maman|Bravo.
 maman|Tu as les mains farineuses ?
 enfant-m|Oui, maman.
 enfant-m|C'est doux.
 narrateur|Ils font un petit pain.
 narrateur|Le petit pain est tout rond.
+maman|Il ressemble à une lune.
+enfant-m|Une petite lune.
+maman|Oui.
+narrateur|Un oiseau chante dehors.
+maman|Tu as entendu l'oiseau ?
+enfant-m|Oui, maman.
 maman|On range la farine ?
 narrateur|Chouchou pousse le bol.
 narrateur|Maman range la cuillère.
 enfant-m|Merci, maman.
 maman|Merci, Chouchou.
 maman|Tu as éteint.
-maman|Tu as choisi un autre jeu.
-maman|C'est du bon travail.</t>
+maman|Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1404,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit fini. Que fait Apolline ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman dit fini. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1572,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1584,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris la pâte. Bravo, Chouchou. Quand on dit fini, on éteint. Puis on prend un autre jeu. La pâte, c'était bien. C'est du bon travail.</t>
+          <t>Maman a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris la pâte. Bravo, Chouchou. Quand on dit fini, on éteint. Puis on prend un autre jeu. La pâte, c'était bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman a dit fini. Apolline a éteint. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. La pâte, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris la pâte. Bravo, Chouchou. Quand on dit fini, on éteint. Puis on prend un autre jeu. La pâte, c'était bien.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,11 +1749,9 @@
 maman|Bravo, Chouchou.
 maman|Quand on dit fini, on éteint.
 maman|Puis on prend un autre jeu.
-narrateur|La pâte, c'était bien.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|La pâte, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1766,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le petit pain repose. Il est tout rond, tout blanc. Merci, maman. Merci, Chouchou. La cuisine est calme. On reste encore un peu ? Oui. Un peu de farine brille encore. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
+          <t>Le petit pain repose. Il est tout rond, tout blanc. Un peu de farine brille encore. Tu as vu le petit nuage ? Oui. Il danse. Merci, maman. Merci, Chouchou. La cuisine est calme. On reste encore un peu ? Oui. La tablette est éteinte. La pâte est là. Il sent bon. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le petit pain repose. Apolline dit merci à maman. La cuisine est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit pain repose. Il est tout rond, tout blanc. Un peu de farine brille encore. Tu as vu le petit nuage ? Oui. Il danse. Merci, maman. Merci, Chouchou. La cuisine est calme. On reste encore un peu ? Oui. La tablette est éteinte. La pâte est là. Il sent bon. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1904,18 +1914,21 @@
         <is>
           <t>narrateur|Le petit pain repose.
 narrateur|Il est tout rond, tout blanc.
+narrateur|Un peu de farine brille encore.
+maman|Tu as vu le petit nuage ?
+enfant-m|Oui.
+enfant-m|Il danse.
 enfant-m|Merci, maman.
 maman|Merci, Chouchou.
 narrateur|La cuisine est calme.
 maman|On reste encore un peu ?
 enfant-m|Oui.
-narrateur|Un peu de farine brille encore.
-maman|Tu as éteint.
-maman|Tu as choisi un autre jeu.
+maman|La tablette est éteinte.
+maman|La pâte est là.
+maman|Il sent bon.
 maman|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1940,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. J'ai éteint. On a pétri la pâte. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Maman a dit fini. J'ai éteint. On a pétri la pâte. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. J'ai éteint. On a pétri la pâte. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2083,12 +2096,9 @@
           <t>enfant-m|Maman a dit fini.
 enfant-m|J'ai éteint.
 enfant-m|On a pétri la pâte.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2107,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-04.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apolline, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
